--- a/실습파일/실습3_파일명일괄변경과_개별메일.xlsx
+++ b/실습파일/실습3_파일명일괄변경과_개별메일.xlsx
@@ -633,7 +633,7 @@
     <row r="3">
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>걸리는 시간: 약 14분   (심화 코스)   |   [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [일반 기능] 안의 세 가지</t>
+          <t>걸리는 시간: 약 14분   (심화 코스)   |   [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [일반 기능] 안의 세 가지</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
     <row r="22" ht="32" customHeight="1" s="21">
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>③ 시작하면 멈출 수 없습니다. 실행이 시작된 뒤에는 ESC로 중단할 수 없습니다. 늘 3~5행만 먼저 돌려 보고 전체를 돌리세요.</t>
+          <t>③ AI 처리는 시작하면 멈출 수 없습니다. 실행이 시작된 뒤에는 ESC로 중단할 수 없습니다(메일 발송은 Esc 로 멈출 수 있습니다). 늘 3~5행만 먼저 돌려 보고 전체를 돌리세요.</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
     <row r="27" ht="22" customHeight="1" s="21">
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [일반 기능] → [폴더 내 파일 목록 가져오기]</t>
+          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [일반 기능] → [폴더 내 파일 목록 가져오기]</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
     <row r="37" ht="22" customHeight="1" s="21">
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>1.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [일반 기능] → [파일 경로로 파일명 변경]</t>
+          <t>1.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [일반 기능] → [파일 경로로 파일명 변경]</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
     <row r="58">
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>1.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [일반 기능] → [메일 자동 발송]     ← 첫 번째 실행</t>
+          <t>1.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [일반 기능] → [메일 자동 발송]     ← 첫 번째 실행</t>
         </is>
       </c>
     </row>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="51" customHeight="1" s="21">
+    <row r="67" ht="64" customHeight="1" s="21">
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>9.  [발송 결과] 시트가 생기고 성공 3건이 기록됩니다. 한 줄마다 시간·서비스·이메일·이름·제목·상태·오류·첨부1~3·메시지ID·소요시간 12가지가 남습니다. F열의 OK / FAIL 에는 색이 칠해지지 않습니다. 색이 들어가는 곳은 맨 아래 초록 줄 하나뿐이라, 실패를 찾으려면 글자를 눈으로 훑어야 합니다. 이 시트는 지워지지 않고 실행할 때마다 아래로 쌓입니다.</t>
+          <t>9.  [발송 결과] 시트가 생기고 성공 3건이 기록됩니다. 한 줄마다 시간·서비스·이메일·이름·제목·상태·오류·첨부1~3·메시지ID·소요(ms) 12칸이 있는데 소요(ms)는 비어 있습니다. F열의 OK / FAIL 에는 색이 칠해지지 않습니다. 색이 들어가는 곳은 맨 아래 초록 줄 하나뿐이라, 실패를 찾으려면 글자를 눈으로 훑어야 합니다. 이 시트는 지워지지 않고 실행할 때마다 아래로 쌓입니다.</t>
         </is>
       </c>
     </row>
